--- a/app/udp_tool/output_excel_reports/pdm/05_Carbon_Calculator_UDP_Migration_Report.xlsx
+++ b/app/udp_tool/output_excel_reports/pdm/05_Carbon_Calculator_UDP_Migration_Report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UDP Definition" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Value Reconciliation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exceptions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="UDP Definition" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Value Reconciliation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Exceptions" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'UDP Definition'!$A$1:$N$1</definedName>
@@ -537,7 +537,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>2026-09-05 21:17:04</t>
+          <t>2026-09-05 20:23:41</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr"/>
@@ -563,7 +563,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\SrinivasaPesala\Desktop\migration-platform_4_sept_final_h_l_m\sappdmodels\pdm\05_Carbon_Calculator.pdm</t>
+          <t>C:\Users\Shivansh\Downloads\migration-platform_4_sept_final\sappdmodels\pdm\05_Carbon_Calculator.pdm</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">

--- a/app/udp_tool/output_excel_reports/pdm/05_Carbon_Calculator_UDP_Migration_Report.xlsx
+++ b/app/udp_tool/output_excel_reports/pdm/05_Carbon_Calculator_UDP_Migration_Report.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>2026-09-03 10:50:47</t>
+          <t>2026-09-05 17:45:21</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr"/>
@@ -563,7 +563,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>c:\Users\SrinivasaPesala\Desktop\migration-platform_v004\app\udp_tool\input_sap_models\05_Carbon_Calculator.pdm</t>
+          <t>C:\Users\SrinivasaPesala\Desktop\migration-platform_4_sept_final_sonar_high\sappdmodels\pdm\05_Carbon_Calculator.pdm</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>c:\Users\SrinivasaPesala\Desktop\migration-platform_v004\app\udp_tool\output_erwin_models\05_Carbon_Calculator.erwin</t>
+          <t>erwinmodels\2_preprocessed\erwin\05_Carbon_Calculator.erwin</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>Created (Entity); Created (Model)</t>
+          <t>Updated (Entity); Updated (Model)</t>
         </is>
       </c>
       <c r="K18" s="6">
@@ -5067,11 +5067,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -5079,12 +5074,17 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -5851,11 +5851,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G65" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -5863,12 +5858,17 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -6682,11 +6682,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G83" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -6694,12 +6689,17 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -7466,11 +7466,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G100" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -7478,12 +7473,17 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -8297,11 +8297,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G118" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -8309,12 +8304,17 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -9118,11 +9118,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G136" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -9130,12 +9125,17 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -9949,11 +9949,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G154" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -9961,12 +9956,17 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -10770,11 +10770,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G172" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -10782,12 +10777,17 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -11591,11 +11591,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G190" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -11603,12 +11598,17 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -12375,11 +12375,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G207" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -12387,12 +12382,17 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -13206,11 +13206,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G225" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -13218,12 +13213,17 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -14027,11 +14027,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G243" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -14039,12 +14034,17 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -14858,11 +14858,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G261" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -14870,12 +14865,17 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -15642,11 +15642,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G278" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -15654,12 +15649,17 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -16426,11 +16426,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G295" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -16438,12 +16433,17 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -17210,11 +17210,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G312" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -17222,12 +17217,17 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -17994,11 +17994,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G329" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -18006,12 +18001,17 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -18778,11 +18778,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F346" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G346" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -18790,12 +18785,17 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -19599,11 +19599,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F364" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G364" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -19611,12 +19606,17 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -20383,11 +20383,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F381" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G381" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -20395,12 +20390,17 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -21167,11 +21167,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F398" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G398" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -21179,12 +21174,17 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -21951,11 +21951,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F415" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G415" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -21963,12 +21958,17 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -22735,11 +22735,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F432" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G432" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -22747,12 +22742,17 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -23519,11 +23519,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F449" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G449" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -23531,12 +23526,17 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -24303,11 +24303,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F466" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G466" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -24315,12 +24310,17 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -25087,11 +25087,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F483" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G483" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -25099,12 +25094,17 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -25918,11 +25918,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F501" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G501" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -25930,12 +25925,17 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -26890,11 +26890,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F522" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G522" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -26902,12 +26897,17 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -27674,11 +27674,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F539" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G539" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -27686,12 +27681,17 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -28458,11 +28458,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F556" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G556" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -28470,12 +28465,17 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -29242,11 +29242,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F573" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G573" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -29254,12 +29249,17 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -30214,11 +30214,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F594" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G594" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -30226,12 +30221,17 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -31035,11 +31035,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F612" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G612" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -31047,12 +31042,17 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -31856,11 +31856,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F630" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G630" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -31868,12 +31863,17 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -32640,11 +32640,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F647" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G647" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -32652,12 +32647,17 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -33461,11 +33461,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F665" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G665" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -33473,12 +33468,17 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J665" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -34245,11 +34245,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F682" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G682" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -34257,12 +34252,17 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -35029,11 +35029,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F699" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G699" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -35041,12 +35036,17 @@
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -35813,11 +35813,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F716" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G716" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -35825,12 +35820,17 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -36597,11 +36597,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F733" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G733" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -36609,12 +36604,17 @@
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -37381,11 +37381,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F750" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G750" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -37393,12 +37388,17 @@
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I750" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -38202,11 +38202,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F768" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G768" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -38214,12 +38209,17 @@
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I768" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J768" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -38986,11 +38986,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F785" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G785" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -38998,12 +38993,17 @@
       </c>
       <c r="H785" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I785" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J785" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -40413,11 +40413,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F816" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G816" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -40425,12 +40420,17 @@
       </c>
       <c r="H816" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I816" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J816" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -64382,11 +64382,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F1338" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G1338" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -64394,12 +64389,17 @@
       </c>
       <c r="H1338" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I1338" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J1338" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -65809,11 +65809,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F1369" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G1369" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -65821,12 +65816,17 @@
       </c>
       <c r="H1369" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I1369" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J1369" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -67236,11 +67236,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F1400" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G1400" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -67248,12 +67243,17 @@
       </c>
       <c r="H1400" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I1400" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J1400" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -68020,11 +68020,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F1417" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G1417" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -68032,12 +68027,17 @@
       </c>
       <c r="H1417" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I1417" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J1417" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -69635,11 +69635,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F1452" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G1452" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -69647,12 +69642,17 @@
       </c>
       <c r="H1452" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I1452" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J1452" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -72991,11 +72991,6 @@
           <t>false</t>
         </is>
       </c>
-      <c r="F1525" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="G1525" t="inlineStr">
         <is>
           <t>Entity</t>
@@ -73003,12 +72998,17 @@
       </c>
       <c r="H1525" t="inlineStr">
         <is>
-          <t>Applied - Verified</t>
+          <t>Skipped - Property Rejected By erwin</t>
         </is>
       </c>
       <c r="I1525" t="inlineStr">
         <is>
-          <t>Match</t>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="J1525" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
     </row>
@@ -76113,7 +76113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -76159,699 +76159,755 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>Empty source value</t>
+          <t>Property rejected by erwin</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>ACTIVITY_CATEGORY_PARAMETER</t>
+          <t>ACTIVITY_CATEGORY</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>DataArea</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>The property exists on the source entity but holds no value.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
-          <t>No action if the property is genuinely blank in PowerDesigner.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Empty source value</t>
+          <t>Property rejected by erwin</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>ACTIVITY_CATEGORY_TYPE</t>
+          <t>ACTIVITY_CATEGORY_DIMENSION</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>DataArea</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>The property exists on the source entity but holds no value.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>No action if the property is genuinely blank in PowerDesigner.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Empty source value</t>
+          <t>Property rejected by erwin</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>ACTIVITY_TYPE_PARAMETER</t>
+          <t>ACTIVITY_CATEGORY_PARAMETER</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>DataArea</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>The property exists on the source entity but holds no value.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>No action if the property is genuinely blank in PowerDesigner.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Empty source value</t>
+          <t>Property rejected by erwin</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>ACTIVITY_TYPE_PARAMETER_FACTOR</t>
+          <t>ACTIVITY_CATEGORY_TYPE</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>DataArea</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>The property exists on the source entity but holds no value.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>No action if the property is genuinely blank in PowerDesigner.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Empty source value</t>
+          <t>Property rejected by erwin</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>DIMENSION</t>
+          <t>ACTIVITY_CATEGORY_TYPE_DIMENSION</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>DataArea</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>The property exists on the source entity but holds no value.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>No action if the property is genuinely blank in PowerDesigner.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Empty source value</t>
+          <t>Property rejected by erwin</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>FUEL_PRODUCT</t>
+          <t>ACTIVITY_TYPE_PARAMETER</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>DataArea</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>The property exists on the source entity but holds no value.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>No action if the property is genuinely blank in PowerDesigner.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Empty source value</t>
+          <t>Property rejected by erwin</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>PRODUCT</t>
+          <t>ACTIVITY_TYPE_PARAMETER_FACTOR</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>DataArea</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>The property exists on the source entity but holds no value.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>No action if the property is genuinely blank in PowerDesigner.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Empty source value</t>
+          <t>Property rejected by erwin</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>PRODUCT_EMISSION_COMPONENT</t>
+          <t>APPLICATION_EQUIPMENT</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>DataArea</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>The property exists on the source entity but holds no value.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>No action if the property is genuinely blank in PowerDesigner.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Empty source value</t>
+          <t>Property rejected by erwin</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>PRODUCT_PROPERTY_VALUE</t>
+          <t>APPLICATION_METHOD</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>DataArea</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>The property exists on the source entity but holds no value.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>No action if the property is genuinely blank in PowerDesigner.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Empty source value</t>
+          <t>Property rejected by erwin</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>PROPERTY_TYPE</t>
+          <t>CLIENT</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>DataArea</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>The property exists on the source entity but holds no value.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>No action if the property is genuinely blank in PowerDesigner.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Inferred value list</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="n"/>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>CLIENT_UOM</t>
+        </is>
+      </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>DesignStatus</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Inferred value list</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="n"/>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>DIMENSION</t>
+        </is>
+      </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>DataCategory</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Inferred value list</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="n"/>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>DIMENSION_VALUE</t>
+        </is>
+      </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>EntityCategory</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Inferred value list</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="n"/>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>EQUIPMENT_ENGINE_TYPE</t>
+        </is>
+      </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Criticality</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Inferred value list</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="n"/>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>EQUIPMENT_TYPE</t>
+        </is>
+      </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>CommerciallySensitiveInformation</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Inferred value list</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="n"/>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>FACTOR_PUBLISHER</t>
+        </is>
+      </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>DataConfidentiality</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Inferred value list</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="n"/>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>FACTOR_SOURCE</t>
+        </is>
+      </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>EntityPersonalData</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Inferred value list</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="n"/>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>FACTOR_SOURCE_COMPOSITION</t>
+        </is>
+      </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>FinancialPersonalData</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Inferred value list</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="n"/>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>FUEL_APPLICATION</t>
+        </is>
+      </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>SensitivePersonalData</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Inferred value list</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="n"/>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>FUEL_FORM</t>
+        </is>
+      </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>MTED_EDaM_Mapping_Note</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Inferred value list</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="n"/>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>FUEL_FORM_QUANTITY_UNIT</t>
+        </is>
+      </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>MappingLevel</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Inferred value list</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="n"/>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>FUEL_MARKET_PRODUCT</t>
+        </is>
+      </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>CSI</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Inferred value list</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="n"/>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>FUEL_PRODUCT</t>
+        </is>
+      </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>MTED_Encryption_Required</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Inferred value list</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="n"/>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>FUEL_PRODUCT_REGION</t>
+        </is>
+      </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
           <t>PII</t>
@@ -76859,402 +76915,1946 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Inferred value list</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="n"/>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>FUEL_PRODUCT_REGION_CLIENT</t>
+        </is>
+      </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>DataArea</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Inferred value list</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="n"/>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>FUEL_PRODUCT_REGION_COMMENT</t>
+        </is>
+      </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>BIM_core_CSI</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Inferred value list</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="n"/>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>GHG</t>
+        </is>
+      </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>EncryptionRequired</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Inferred value list</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="n"/>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>LIFECYCLE_PHASE</t>
+        </is>
+      </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>MaskingRequired</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Inferred value list</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="n"/>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>LNG_ENGINE_TYPE</t>
+        </is>
+      </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>BIM_core_PII</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Inferred value list</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="n"/>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>NCI_CLIENT_PARAMETER</t>
+        </is>
+      </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Attribute_1</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Inferred value list</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="n"/>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>NCI_CLIENT_PARAMETER_VALUE_SET</t>
+        </is>
+      </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>MTED_EDaM_Entity_Critical_Data</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Inferred value list</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="n"/>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>NCI_CLIENT_PRODUCT_FACTOR</t>
+        </is>
+      </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>MTED_EDaM_Security_Classification</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Inferred value list</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="n"/>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>NCI_CLIENT_PRODUCT_TYPE</t>
+        </is>
+      </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>MTED_EDaM_Design_Status</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Inferred value list</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="n"/>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>PARAMETER_TYPE</t>
+        </is>
+      </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>MTED_EDaM_Entity_Data_Category</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Inferred value list</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="n"/>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>PARAMETER_VALUE_SET</t>
+        </is>
+      </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>MTED_EDaM_Mapping_Level</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Not carried by the erwin bridge</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="n"/>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>PCF_CLIENT_DIMENSION_VALUE</t>
+        </is>
+      </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Glossary term bindings (UseTerm)</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>2 term shortcuts - NOT delivered - external .glm has no erwin equivalent</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>NOT RECOVERABLE as-is. SOW covers under 'naming standards, macros, templates - not automatically migrated'. Re-establish in erwin Naming Standards or relocate to Collibra.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Not carried by the erwin bridge</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="n"/>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>PCF_CLIENT_PRODUCT</t>
+        </is>
+      </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>GTL templates (relationship assertion, FK naming)</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>0 - NOT delivered</t>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>NOT RECOVERABLE. SOW covers under 'model macros - manual rewrite required'.</t>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>PRODUCT_EMISSION_COMPONENT</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>PII</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>PRODUCT_EMISSION_COMPONENT_HISTORY</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>PII</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>PRODUCT_PROPERTY_VALUE</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>PII</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>PROPERTY_TYPE</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>PII</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>REQ_NCI_CLIENT_PARAMETER</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>PII</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>REQ_NCI_CLIENT_PARAMETER_VALUE_SET</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>PII</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>REQ_NCI_CLIENT_PRODUCT_FACTOR</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>PII</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>REQ_NCI_CLIENT_PRODUCT_TYPE</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>PII</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>REQ_PCF_FUEL_PRODUCT_REGION_CLIENT</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>PII</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>UOM</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>PII</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>UOM_CONVERSION</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>PII</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>UOM_CONVERSION_TYPE</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>PII</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>Property rejected by erwin</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>UOM_DERIVATION</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>PII</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>erwin accepted none of the known property name formats for this UDP on this object.</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>Check the UDP exists in the erwin dictionary for this owner type (Entity vs Model).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>Empty source value</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVITY_CATEGORY_PARAMETER</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>DataArea</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>The property exists on the source entity but holds no value.</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>No action if the property is genuinely blank in PowerDesigner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>Empty source value</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVITY_CATEGORY_TYPE</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>DataArea</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>The property exists on the source entity but holds no value.</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>No action if the property is genuinely blank in PowerDesigner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>Empty source value</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVITY_TYPE_PARAMETER</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>DataArea</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>The property exists on the source entity but holds no value.</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>No action if the property is genuinely blank in PowerDesigner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>Empty source value</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVITY_TYPE_PARAMETER_FACTOR</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>DataArea</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>The property exists on the source entity but holds no value.</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>No action if the property is genuinely blank in PowerDesigner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Empty source value</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>DIMENSION</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>DataArea</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>The property exists on the source entity but holds no value.</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>No action if the property is genuinely blank in PowerDesigner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Empty source value</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>FUEL_PRODUCT</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>DataArea</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>The property exists on the source entity but holds no value.</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>No action if the property is genuinely blank in PowerDesigner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>Empty source value</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>PRODUCT</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>DataArea</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>The property exists on the source entity but holds no value.</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>No action if the property is genuinely blank in PowerDesigner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Empty source value</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>PRODUCT_EMISSION_COMPONENT</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>DataArea</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>The property exists on the source entity but holds no value.</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>No action if the property is genuinely blank in PowerDesigner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>Empty source value</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>PRODUCT_PROPERTY_VALUE</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>DataArea</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>The property exists on the source entity but holds no value.</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>No action if the property is genuinely blank in PowerDesigner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>Empty source value</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>PROPERTY_TYPE</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>DataArea</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>The property exists on the source entity but holds no value.</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>No action if the property is genuinely blank in PowerDesigner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>Inferred value list</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>DesignStatus</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>Inferred value list</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="n"/>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>DataCategory</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>Inferred value list</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="n"/>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>EntityCategory</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>Inferred value list</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="n"/>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>Criticality</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>Inferred value list</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="n"/>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>CommerciallySensitiveInformation</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>Inferred value list</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="n"/>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>DataConfidentiality</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>Inferred value list</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="n"/>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>EntityPersonalData</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>Inferred value list</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="n"/>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>FinancialPersonalData</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>Inferred value list</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="n"/>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>SensitivePersonalData</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>Inferred value list</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="n"/>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>MTED_EDaM_Mapping_Note</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>Inferred value list</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="n"/>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>MappingLevel</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>Inferred value list</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="n"/>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>CSI</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>Inferred value list</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="n"/>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>MTED_Encryption_Required</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>Inferred value list</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="n"/>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>PII</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>Inferred value list</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="n"/>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>DataArea</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>Inferred value list</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="n"/>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>BIM_core_CSI</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>Inferred value list</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="n"/>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>EncryptionRequired</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>Inferred value list</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="n"/>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>MaskingRequired</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>Inferred value list</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="n"/>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>BIM_core_PII</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>Inferred value list</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="n"/>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>Attribute_1</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>Inferred value list</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="n"/>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>MTED_EDaM_Entity_Critical_Data</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>Inferred value list</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="n"/>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>MTED_EDaM_Security_Classification</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>Inferred value list</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="n"/>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>MTED_EDaM_Design_Status</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>Inferred value list</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="n"/>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>MTED_EDaM_Entity_Data_Category</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>Inferred value list</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="n"/>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>MTED_EDaM_Mapping_Level</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>The permitted values were inferred from observed data, not from BIM-core.xem. Observed is not the same as permitted.</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>Confirm the list against BIM-core.xem before sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
           <t>Informational</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>Not carried by the erwin bridge</t>
         </is>
       </c>
-      <c r="C39" s="6" t="n"/>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="C87" s="6" t="n"/>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>Glossary term bindings (UseTerm)</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>2 term shortcuts - NOT delivered - external .glm has no erwin equivalent</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>NOT RECOVERABLE as-is. SOW covers under 'naming standards, macros, templates - not automatically migrated'. Re-establish in erwin Naming Standards or relocate to Collibra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>Not carried by the erwin bridge</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="n"/>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>GTL templates (relationship assertion, FK naming)</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>0 - NOT delivered</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>NOT RECOVERABLE. SOW covers under 'model macros - manual rewrite required'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>Not carried by the erwin bridge</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="n"/>
+      <c r="D89" s="6" t="inlineStr">
         <is>
           <t>Repository version history / branch</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E89" s="6" t="inlineStr">
         <is>
           <t>extraction n/a - NOT delivered - point-in-time extract only</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <t>OUT OF SCOPE per SOW: 'version history &amp; audit lineage lost'. Archive PD repository read-only.</t>
         </is>
